--- a/joueurs_services.xlsx
+++ b/joueurs_services.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="221">
   <si>
     <t>Prénom</t>
   </si>
@@ -1173,6 +1173,9 @@
       <c r="B15" t="s">
         <v>34</v>
       </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
@@ -1291,6 +1294,9 @@
       <c r="B26" t="s">
         <v>53</v>
       </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
@@ -1376,6 +1382,9 @@
       <c r="B34" t="s">
         <v>70</v>
       </c>
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
@@ -1417,6 +1426,9 @@
       <c r="B38" t="s">
         <v>79</v>
       </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
@@ -1744,6 +1756,9 @@
       <c r="B68" t="s">
         <v>139</v>
       </c>
+      <c r="C68" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
@@ -1763,6 +1778,9 @@
       <c r="B70" t="s">
         <v>143</v>
       </c>
+      <c r="C70" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
@@ -1913,6 +1931,9 @@
       </c>
       <c r="B84" t="s">
         <v>170</v>
+      </c>
+      <c r="C84" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="85" spans="1:3">

--- a/joueurs_services.xlsx
+++ b/joueurs_services.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="220">
   <si>
     <t>Prénom</t>
   </si>
@@ -236,9 +236,6 @@
   </si>
   <si>
     <t>Fethinho</t>
-  </si>
-  <si>
-    <t>IT</t>
   </si>
   <si>
     <t>Filipe</t>
@@ -1394,37 +1391,37 @@
         <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" t="s">
         <v>74</v>
       </c>
-      <c r="B36" t="s">
-        <v>75</v>
-      </c>
       <c r="C36" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" t="s">
         <v>76</v>
       </c>
-      <c r="B37" t="s">
-        <v>77</v>
-      </c>
       <c r="C37" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" t="s">
         <v>78</v>
-      </c>
-      <c r="B38" t="s">
-        <v>79</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -1432,10 +1429,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" t="s">
         <v>80</v>
-      </c>
-      <c r="B39" t="s">
-        <v>81</v>
       </c>
       <c r="C39" t="s">
         <v>12</v>
@@ -1443,10 +1440,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" t="s">
         <v>82</v>
-      </c>
-      <c r="B40" t="s">
-        <v>83</v>
       </c>
       <c r="C40" t="s">
         <v>20</v>
@@ -1454,10 +1451,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41" t="s">
         <v>84</v>
-      </c>
-      <c r="B41" t="s">
-        <v>85</v>
       </c>
       <c r="C41" t="s">
         <v>20</v>
@@ -1465,10 +1462,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" t="s">
         <v>86</v>
-      </c>
-      <c r="B42" t="s">
-        <v>87</v>
       </c>
       <c r="C42" t="s">
         <v>20</v>
@@ -1476,10 +1473,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
+        <v>87</v>
+      </c>
+      <c r="B43" t="s">
         <v>88</v>
-      </c>
-      <c r="B43" t="s">
-        <v>89</v>
       </c>
       <c r="C43" t="s">
         <v>20</v>
@@ -1487,10 +1484,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
+        <v>89</v>
+      </c>
+      <c r="B44" t="s">
         <v>90</v>
-      </c>
-      <c r="B44" t="s">
-        <v>91</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
@@ -1498,10 +1495,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45" t="s">
         <v>92</v>
-      </c>
-      <c r="B45" t="s">
-        <v>93</v>
       </c>
       <c r="C45" t="s">
         <v>58</v>
@@ -1509,10 +1506,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
+        <v>93</v>
+      </c>
+      <c r="B46" t="s">
         <v>94</v>
-      </c>
-      <c r="B46" t="s">
-        <v>95</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
@@ -1520,10 +1517,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
+        <v>95</v>
+      </c>
+      <c r="B47" t="s">
         <v>96</v>
-      </c>
-      <c r="B47" t="s">
-        <v>97</v>
       </c>
       <c r="C47" t="s">
         <v>7</v>
@@ -1531,10 +1528,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" t="s">
         <v>98</v>
-      </c>
-      <c r="B48" t="s">
-        <v>99</v>
       </c>
       <c r="C48" t="s">
         <v>12</v>
@@ -1542,10 +1539,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
+        <v>99</v>
+      </c>
+      <c r="B49" t="s">
         <v>100</v>
-      </c>
-      <c r="B49" t="s">
-        <v>101</v>
       </c>
       <c r="C49" t="s">
         <v>12</v>
@@ -1553,10 +1550,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
+        <v>101</v>
+      </c>
+      <c r="B50" t="s">
         <v>102</v>
-      </c>
-      <c r="B50" t="s">
-        <v>103</v>
       </c>
       <c r="C50" t="s">
         <v>17</v>
@@ -1564,10 +1561,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" t="s">
         <v>104</v>
-      </c>
-      <c r="B51" t="s">
-        <v>105</v>
       </c>
       <c r="C51" t="s">
         <v>17</v>
@@ -1575,10 +1572,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B52" t="s">
         <v>106</v>
-      </c>
-      <c r="B52" t="s">
-        <v>107</v>
       </c>
       <c r="C52" t="s">
         <v>20</v>
@@ -1586,10 +1583,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
+        <v>107</v>
+      </c>
+      <c r="B53" t="s">
         <v>108</v>
-      </c>
-      <c r="B53" t="s">
-        <v>109</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
@@ -1597,10 +1594,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
+        <v>109</v>
+      </c>
+      <c r="B54" t="s">
         <v>110</v>
-      </c>
-      <c r="B54" t="s">
-        <v>111</v>
       </c>
       <c r="C54" t="s">
         <v>12</v>
@@ -1608,10 +1605,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
+        <v>111</v>
+      </c>
+      <c r="B55" t="s">
         <v>112</v>
-      </c>
-      <c r="B55" t="s">
-        <v>113</v>
       </c>
       <c r="C55" t="s">
         <v>20</v>
@@ -1619,10 +1616,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
+        <v>113</v>
+      </c>
+      <c r="B56" t="s">
         <v>114</v>
-      </c>
-      <c r="B56" t="s">
-        <v>115</v>
       </c>
       <c r="C56" t="s">
         <v>20</v>
@@ -1630,10 +1627,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
+        <v>115</v>
+      </c>
+      <c r="B57" t="s">
         <v>116</v>
-      </c>
-      <c r="B57" t="s">
-        <v>117</v>
       </c>
       <c r="C57" t="s">
         <v>12</v>
@@ -1641,10 +1638,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
+        <v>117</v>
+      </c>
+      <c r="B58" t="s">
         <v>118</v>
-      </c>
-      <c r="B58" t="s">
-        <v>119</v>
       </c>
       <c r="C58" t="s">
         <v>12</v>
@@ -1652,10 +1649,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
+        <v>119</v>
+      </c>
+      <c r="B59" t="s">
         <v>120</v>
-      </c>
-      <c r="B59" t="s">
-        <v>121</v>
       </c>
       <c r="C59" t="s">
         <v>12</v>
@@ -1663,10 +1660,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
+        <v>121</v>
+      </c>
+      <c r="B60" t="s">
         <v>122</v>
-      </c>
-      <c r="B60" t="s">
-        <v>123</v>
       </c>
       <c r="C60" t="s">
         <v>17</v>
@@ -1674,10 +1671,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
+        <v>123</v>
+      </c>
+      <c r="B61" t="s">
         <v>124</v>
-      </c>
-      <c r="B61" t="s">
-        <v>125</v>
       </c>
       <c r="C61" t="s">
         <v>7</v>
@@ -1685,10 +1682,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
+        <v>125</v>
+      </c>
+      <c r="B62" t="s">
         <v>126</v>
-      </c>
-      <c r="B62" t="s">
-        <v>127</v>
       </c>
       <c r="C62" t="s">
         <v>12</v>
@@ -1696,10 +1693,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
+        <v>127</v>
+      </c>
+      <c r="B63" t="s">
         <v>128</v>
-      </c>
-      <c r="B63" t="s">
-        <v>129</v>
       </c>
       <c r="C63" t="s">
         <v>17</v>
@@ -1707,10 +1704,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
+        <v>129</v>
+      </c>
+      <c r="B64" t="s">
         <v>130</v>
-      </c>
-      <c r="B64" t="s">
-        <v>131</v>
       </c>
       <c r="C64" t="s">
         <v>20</v>
@@ -1718,10 +1715,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" t="s">
         <v>132</v>
-      </c>
-      <c r="B65" t="s">
-        <v>133</v>
       </c>
       <c r="C65" t="s">
         <v>7</v>
@@ -1729,10 +1726,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
+        <v>133</v>
+      </c>
+      <c r="B66" t="s">
         <v>134</v>
-      </c>
-      <c r="B66" t="s">
-        <v>135</v>
       </c>
       <c r="C66" t="s">
         <v>20</v>
@@ -1740,10 +1737,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
+        <v>135</v>
+      </c>
+      <c r="B67" t="s">
         <v>136</v>
-      </c>
-      <c r="B67" t="s">
-        <v>137</v>
       </c>
       <c r="C67" t="s">
         <v>17</v>
@@ -1751,10 +1748,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
+        <v>137</v>
+      </c>
+      <c r="B68" t="s">
         <v>138</v>
-      </c>
-      <c r="B68" t="s">
-        <v>139</v>
       </c>
       <c r="C68" t="s">
         <v>58</v>
@@ -1762,10 +1759,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
+        <v>139</v>
+      </c>
+      <c r="B69" t="s">
         <v>140</v>
-      </c>
-      <c r="B69" t="s">
-        <v>141</v>
       </c>
       <c r="C69" t="s">
         <v>7</v>
@@ -1773,10 +1770,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
+        <v>141</v>
+      </c>
+      <c r="B70" t="s">
         <v>142</v>
-      </c>
-      <c r="B70" t="s">
-        <v>143</v>
       </c>
       <c r="C70" t="s">
         <v>17</v>
@@ -1784,10 +1781,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
+        <v>143</v>
+      </c>
+      <c r="B71" t="s">
         <v>144</v>
-      </c>
-      <c r="B71" t="s">
-        <v>145</v>
       </c>
       <c r="C71" t="s">
         <v>20</v>
@@ -1795,10 +1792,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" t="s">
         <v>146</v>
-      </c>
-      <c r="B72" t="s">
-        <v>147</v>
       </c>
       <c r="C72" t="s">
         <v>7</v>
@@ -1806,10 +1803,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
+        <v>147</v>
+      </c>
+      <c r="B73" t="s">
         <v>148</v>
-      </c>
-      <c r="B73" t="s">
-        <v>149</v>
       </c>
       <c r="C73" t="s">
         <v>7</v>
@@ -1817,10 +1814,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
+        <v>149</v>
+      </c>
+      <c r="B74" t="s">
         <v>150</v>
-      </c>
-      <c r="B74" t="s">
-        <v>151</v>
       </c>
       <c r="C74" t="s">
         <v>58</v>
@@ -1828,10 +1825,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
+        <v>151</v>
+      </c>
+      <c r="B75" t="s">
         <v>152</v>
-      </c>
-      <c r="B75" t="s">
-        <v>153</v>
       </c>
       <c r="C75" t="s">
         <v>7</v>
@@ -1839,10 +1836,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
+        <v>153</v>
+      </c>
+      <c r="B76" t="s">
         <v>154</v>
-      </c>
-      <c r="B76" t="s">
-        <v>155</v>
       </c>
       <c r="C76" t="s">
         <v>17</v>
@@ -1850,10 +1847,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C77" t="s">
         <v>20</v>
@@ -1861,10 +1858,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
+        <v>156</v>
+      </c>
+      <c r="B78" t="s">
         <v>157</v>
-      </c>
-      <c r="B78" t="s">
-        <v>158</v>
       </c>
       <c r="C78" t="s">
         <v>7</v>
@@ -1872,10 +1869,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
+        <v>158</v>
+      </c>
+      <c r="B79" t="s">
         <v>159</v>
-      </c>
-      <c r="B79" t="s">
-        <v>160</v>
       </c>
       <c r="C79" t="s">
         <v>17</v>
@@ -1883,10 +1880,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
+        <v>160</v>
+      </c>
+      <c r="B80" t="s">
         <v>161</v>
-      </c>
-      <c r="B80" t="s">
-        <v>162</v>
       </c>
       <c r="C80" t="s">
         <v>12</v>
@@ -1894,10 +1891,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
+        <v>162</v>
+      </c>
+      <c r="B81" t="s">
         <v>163</v>
-      </c>
-      <c r="B81" t="s">
-        <v>164</v>
       </c>
       <c r="C81" t="s">
         <v>20</v>
@@ -1905,10 +1902,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
+        <v>164</v>
+      </c>
+      <c r="B82" t="s">
         <v>165</v>
-      </c>
-      <c r="B82" t="s">
-        <v>166</v>
       </c>
       <c r="C82" t="s">
         <v>7</v>
@@ -1916,10 +1913,10 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
+        <v>166</v>
+      </c>
+      <c r="B83" t="s">
         <v>167</v>
-      </c>
-      <c r="B83" t="s">
-        <v>168</v>
       </c>
       <c r="C83" t="s">
         <v>12</v>
@@ -1927,21 +1924,21 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
+        <v>168</v>
+      </c>
+      <c r="B84" t="s">
         <v>169</v>
       </c>
-      <c r="B84" t="s">
-        <v>170</v>
-      </c>
       <c r="C84" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
+        <v>170</v>
+      </c>
+      <c r="B85" t="s">
         <v>171</v>
-      </c>
-      <c r="B85" t="s">
-        <v>172</v>
       </c>
       <c r="C85" t="s">
         <v>7</v>
@@ -1949,10 +1946,10 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
+        <v>172</v>
+      </c>
+      <c r="B86" t="s">
         <v>173</v>
-      </c>
-      <c r="B86" t="s">
-        <v>174</v>
       </c>
       <c r="C86" t="s">
         <v>20</v>
@@ -1960,10 +1957,10 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
+        <v>174</v>
+      </c>
+      <c r="B87" t="s">
         <v>175</v>
-      </c>
-      <c r="B87" t="s">
-        <v>176</v>
       </c>
       <c r="C87" t="s">
         <v>12</v>
@@ -1971,10 +1968,10 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
+        <v>176</v>
+      </c>
+      <c r="B88" t="s">
         <v>177</v>
-      </c>
-      <c r="B88" t="s">
-        <v>178</v>
       </c>
       <c r="C88" t="s">
         <v>17</v>
@@ -1982,10 +1979,10 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
+        <v>178</v>
+      </c>
+      <c r="B89" t="s">
         <v>179</v>
-      </c>
-      <c r="B89" t="s">
-        <v>180</v>
       </c>
       <c r="C89" t="s">
         <v>12</v>
@@ -1993,10 +1990,10 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B90" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C90" t="s">
         <v>12</v>
@@ -2004,10 +2001,10 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
+        <v>181</v>
+      </c>
+      <c r="B91" t="s">
         <v>182</v>
-      </c>
-      <c r="B91" t="s">
-        <v>183</v>
       </c>
       <c r="C91" t="s">
         <v>12</v>
@@ -2015,10 +2012,10 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
+        <v>183</v>
+      </c>
+      <c r="B92" t="s">
         <v>184</v>
-      </c>
-      <c r="B92" t="s">
-        <v>185</v>
       </c>
       <c r="C92" t="s">
         <v>20</v>
@@ -2026,10 +2023,10 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C93" t="s">
         <v>20</v>
@@ -2037,10 +2034,10 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" t="s">
+        <v>186</v>
+      </c>
+      <c r="B94" t="s">
         <v>187</v>
-      </c>
-      <c r="B94" t="s">
-        <v>188</v>
       </c>
       <c r="C94" t="s">
         <v>17</v>
@@ -2048,10 +2045,10 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
+        <v>188</v>
+      </c>
+      <c r="B95" t="s">
         <v>189</v>
-      </c>
-      <c r="B95" t="s">
-        <v>190</v>
       </c>
       <c r="C95" t="s">
         <v>20</v>
@@ -2059,21 +2056,21 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" t="s">
+        <v>190</v>
+      </c>
+      <c r="B96" t="s">
         <v>191</v>
       </c>
-      <c r="B96" t="s">
-        <v>192</v>
-      </c>
       <c r="C96" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
+        <v>192</v>
+      </c>
+      <c r="B97" t="s">
         <v>193</v>
-      </c>
-      <c r="B97" t="s">
-        <v>194</v>
       </c>
       <c r="C97" t="s">
         <v>12</v>
@@ -2081,10 +2078,10 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
+        <v>194</v>
+      </c>
+      <c r="B98" t="s">
         <v>195</v>
-      </c>
-      <c r="B98" t="s">
-        <v>196</v>
       </c>
       <c r="C98" t="s">
         <v>20</v>
@@ -2092,10 +2089,10 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
+        <v>196</v>
+      </c>
+      <c r="B99" t="s">
         <v>197</v>
-      </c>
-      <c r="B99" t="s">
-        <v>198</v>
       </c>
       <c r="C99" t="s">
         <v>12</v>
@@ -2103,10 +2100,10 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" t="s">
         <v>199</v>
-      </c>
-      <c r="B100" t="s">
-        <v>200</v>
       </c>
       <c r="C100" t="s">
         <v>58</v>
@@ -2114,10 +2111,10 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" t="s">
+        <v>200</v>
+      </c>
+      <c r="B101" t="s">
         <v>201</v>
-      </c>
-      <c r="B101" t="s">
-        <v>202</v>
       </c>
       <c r="C101" t="s">
         <v>58</v>
@@ -2125,10 +2122,10 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
+        <v>202</v>
+      </c>
+      <c r="B102" t="s">
         <v>203</v>
-      </c>
-      <c r="B102" t="s">
-        <v>204</v>
       </c>
       <c r="C102" t="s">
         <v>20</v>
@@ -2136,21 +2133,21 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
+        <v>204</v>
+      </c>
+      <c r="B103" t="s">
         <v>205</v>
       </c>
-      <c r="B103" t="s">
-        <v>206</v>
-      </c>
       <c r="C103" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
+        <v>206</v>
+      </c>
+      <c r="B104" t="s">
         <v>207</v>
-      </c>
-      <c r="B104" t="s">
-        <v>208</v>
       </c>
       <c r="C104" t="s">
         <v>12</v>
@@ -2158,10 +2155,10 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" t="s">
+        <v>208</v>
+      </c>
+      <c r="B105" t="s">
         <v>209</v>
-      </c>
-      <c r="B105" t="s">
-        <v>210</v>
       </c>
       <c r="C105" t="s">
         <v>20</v>
@@ -2169,18 +2166,18 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" t="s">
+        <v>210</v>
+      </c>
+      <c r="B106" t="s">
         <v>211</v>
-      </c>
-      <c r="B106" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
+        <v>212</v>
+      </c>
+      <c r="B107" t="s">
         <v>213</v>
-      </c>
-      <c r="B107" t="s">
-        <v>214</v>
       </c>
       <c r="C107" t="s">
         <v>7</v>
@@ -2188,29 +2185,29 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
+        <v>214</v>
+      </c>
+      <c r="B108" t="s">
         <v>215</v>
-      </c>
-      <c r="B108" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
+        <v>216</v>
+      </c>
+      <c r="B109" t="s">
         <v>217</v>
       </c>
-      <c r="B109" t="s">
-        <v>218</v>
-      </c>
       <c r="C109" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
+        <v>218</v>
+      </c>
+      <c r="B110" t="s">
         <v>219</v>
-      </c>
-      <c r="B110" t="s">
-        <v>220</v>
       </c>
       <c r="C110" t="s">
         <v>58</v>

--- a/joueurs_services.xlsx
+++ b/joueurs_services.xlsx
@@ -2150,7 +2150,7 @@
         <v>207</v>
       </c>
       <c r="C104" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105" spans="1:3">

--- a/joueurs_services.xlsx
+++ b/joueurs_services.xlsx
@@ -1996,7 +1996,7 @@
         <v>180</v>
       </c>
       <c r="C90" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91" spans="1:3">

--- a/joueurs_services.xlsx
+++ b/joueurs_services.xlsx
@@ -1008,6 +1008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -1034,7 +1035,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" hidden="1">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1045,7 +1046,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" hidden="1">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1056,7 +1057,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" hidden="1">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1067,7 +1068,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" hidden="1">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1078,7 +1079,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" hidden="1">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1089,7 +1090,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" hidden="1">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1100,7 +1101,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" hidden="1">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1111,7 +1112,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" hidden="1">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1122,7 +1123,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" hidden="1">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1141,7 +1142,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" hidden="1">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1152,7 +1153,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" hidden="1">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1163,7 +1164,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" hidden="1">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1174,7 +1175,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" hidden="1">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -1185,7 +1186,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" hidden="1">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1196,7 +1197,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" hidden="1">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1207,7 +1208,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" hidden="1">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1218,7 +1219,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" hidden="1">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -1229,7 +1230,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" hidden="1">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -1240,7 +1241,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" hidden="1">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -1251,7 +1252,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" hidden="1">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1262,7 +1263,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" hidden="1">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -1273,7 +1274,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" hidden="1">
       <c r="A25" t="s">
         <v>51</v>
       </c>
@@ -1284,7 +1285,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" hidden="1">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -1295,7 +1296,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" hidden="1">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -1306,7 +1307,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" hidden="1">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -1317,7 +1318,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" hidden="1">
       <c r="A29" t="s">
         <v>59</v>
       </c>
@@ -1328,7 +1329,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" hidden="1">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1339,7 +1340,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" hidden="1">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1350,7 +1351,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" hidden="1">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1362,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" hidden="1">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1372,7 +1373,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" hidden="1">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1383,7 +1384,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" hidden="1">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1394,7 +1395,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" hidden="1">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1405,7 +1406,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" hidden="1">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1416,7 +1417,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" hidden="1">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1427,7 +1428,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" hidden="1">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1438,7 +1439,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" hidden="1">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1449,7 +1450,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" hidden="1">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1460,7 +1461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" hidden="1">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1471,7 +1472,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" hidden="1">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1482,7 +1483,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" hidden="1">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1493,7 +1494,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" hidden="1">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1504,7 +1505,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" hidden="1">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1515,7 +1516,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" hidden="1">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1526,7 +1527,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" hidden="1">
       <c r="A48" t="s">
         <v>97</v>
       </c>
@@ -1537,7 +1538,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" hidden="1">
       <c r="A49" t="s">
         <v>99</v>
       </c>
@@ -1548,7 +1549,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" hidden="1">
       <c r="A50" t="s">
         <v>101</v>
       </c>
@@ -1559,7 +1560,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" hidden="1">
       <c r="A51" t="s">
         <v>103</v>
       </c>
@@ -1570,7 +1571,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" hidden="1">
       <c r="A52" t="s">
         <v>105</v>
       </c>
@@ -1581,7 +1582,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" hidden="1">
       <c r="A53" t="s">
         <v>107</v>
       </c>
@@ -1592,7 +1593,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" hidden="1">
       <c r="A54" t="s">
         <v>109</v>
       </c>
@@ -1603,7 +1604,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" hidden="1">
       <c r="A55" t="s">
         <v>111</v>
       </c>
@@ -1614,7 +1615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" hidden="1">
       <c r="A56" t="s">
         <v>113</v>
       </c>
@@ -1625,7 +1626,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" hidden="1">
       <c r="A57" t="s">
         <v>115</v>
       </c>
@@ -1636,7 +1637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" hidden="1">
       <c r="A58" t="s">
         <v>117</v>
       </c>
@@ -1647,7 +1648,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" hidden="1">
       <c r="A59" t="s">
         <v>119</v>
       </c>
@@ -1658,7 +1659,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" hidden="1">
       <c r="A60" t="s">
         <v>121</v>
       </c>
@@ -1669,7 +1670,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" hidden="1">
       <c r="A61" t="s">
         <v>123</v>
       </c>
@@ -1680,7 +1681,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" hidden="1">
       <c r="A62" t="s">
         <v>125</v>
       </c>
@@ -1691,7 +1692,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" hidden="1">
       <c r="A63" t="s">
         <v>127</v>
       </c>
@@ -1702,7 +1703,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" hidden="1">
       <c r="A64" t="s">
         <v>129</v>
       </c>
@@ -1713,7 +1714,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" hidden="1">
       <c r="A65" t="s">
         <v>131</v>
       </c>
@@ -1724,7 +1725,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" hidden="1">
       <c r="A66" t="s">
         <v>133</v>
       </c>
@@ -1735,7 +1736,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" hidden="1">
       <c r="A67" t="s">
         <v>135</v>
       </c>
@@ -1746,7 +1747,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" hidden="1">
       <c r="A68" t="s">
         <v>137</v>
       </c>
@@ -1757,7 +1758,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" hidden="1">
       <c r="A69" t="s">
         <v>139</v>
       </c>
@@ -1768,7 +1769,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" hidden="1">
       <c r="A70" t="s">
         <v>141</v>
       </c>
@@ -1779,7 +1780,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" hidden="1">
       <c r="A71" t="s">
         <v>143</v>
       </c>
@@ -1790,7 +1791,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" hidden="1">
       <c r="A72" t="s">
         <v>145</v>
       </c>
@@ -1801,7 +1802,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" hidden="1">
       <c r="A73" t="s">
         <v>147</v>
       </c>
@@ -1812,7 +1813,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" hidden="1">
       <c r="A74" t="s">
         <v>149</v>
       </c>
@@ -1823,7 +1824,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" hidden="1">
       <c r="A75" t="s">
         <v>151</v>
       </c>
@@ -1834,7 +1835,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" hidden="1">
       <c r="A76" t="s">
         <v>153</v>
       </c>
@@ -1845,7 +1846,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" hidden="1">
       <c r="A77" t="s">
         <v>153</v>
       </c>
@@ -1856,7 +1857,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" hidden="1">
       <c r="A78" t="s">
         <v>156</v>
       </c>
@@ -1867,7 +1868,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" hidden="1">
       <c r="A79" t="s">
         <v>158</v>
       </c>
@@ -1878,7 +1879,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" hidden="1">
       <c r="A80" t="s">
         <v>160</v>
       </c>
@@ -1889,7 +1890,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" hidden="1">
       <c r="A81" t="s">
         <v>162</v>
       </c>
@@ -1900,7 +1901,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" hidden="1">
       <c r="A82" t="s">
         <v>164</v>
       </c>
@@ -1911,7 +1912,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" hidden="1">
       <c r="A83" t="s">
         <v>166</v>
       </c>
@@ -1922,7 +1923,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" hidden="1">
       <c r="A84" t="s">
         <v>168</v>
       </c>
@@ -1933,7 +1934,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" hidden="1">
       <c r="A85" t="s">
         <v>170</v>
       </c>
@@ -1944,7 +1945,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" hidden="1">
       <c r="A86" t="s">
         <v>172</v>
       </c>
@@ -1955,7 +1956,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" hidden="1">
       <c r="A87" t="s">
         <v>174</v>
       </c>
@@ -1966,7 +1967,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" hidden="1">
       <c r="A88" t="s">
         <v>176</v>
       </c>
@@ -1977,7 +1978,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" hidden="1">
       <c r="A89" t="s">
         <v>178</v>
       </c>
@@ -1988,7 +1989,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" hidden="1">
       <c r="A90" t="s">
         <v>178</v>
       </c>
@@ -1999,7 +2000,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" hidden="1">
       <c r="A91" t="s">
         <v>181</v>
       </c>
@@ -2010,7 +2011,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" hidden="1">
       <c r="A92" t="s">
         <v>183</v>
       </c>
@@ -2021,7 +2022,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" hidden="1">
       <c r="A93" t="s">
         <v>185</v>
       </c>
@@ -2032,7 +2033,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" hidden="1">
       <c r="A94" t="s">
         <v>186</v>
       </c>
@@ -2043,7 +2044,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" hidden="1">
       <c r="A95" t="s">
         <v>188</v>
       </c>
@@ -2054,7 +2055,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" hidden="1">
       <c r="A96" t="s">
         <v>190</v>
       </c>
@@ -2065,7 +2066,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" hidden="1">
       <c r="A97" t="s">
         <v>192</v>
       </c>
@@ -2076,7 +2077,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" hidden="1">
       <c r="A98" t="s">
         <v>194</v>
       </c>
@@ -2087,7 +2088,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" hidden="1">
       <c r="A99" t="s">
         <v>196</v>
       </c>
@@ -2098,7 +2099,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" hidden="1">
       <c r="A100" t="s">
         <v>198</v>
       </c>
@@ -2109,7 +2110,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" hidden="1">
       <c r="A101" t="s">
         <v>200</v>
       </c>
@@ -2120,7 +2121,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" hidden="1">
       <c r="A102" t="s">
         <v>202</v>
       </c>
@@ -2131,7 +2132,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" hidden="1">
       <c r="A103" t="s">
         <v>204</v>
       </c>
@@ -2142,7 +2143,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" hidden="1">
       <c r="A104" t="s">
         <v>206</v>
       </c>
@@ -2153,7 +2154,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" hidden="1">
       <c r="A105" t="s">
         <v>208</v>
       </c>
@@ -2172,7 +2173,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" hidden="1">
       <c r="A107" t="s">
         <v>212</v>
       </c>
@@ -2191,7 +2192,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" hidden="1">
       <c r="A109" t="s">
         <v>216</v>
       </c>
@@ -2202,7 +2203,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" hidden="1">
       <c r="A110" t="s">
         <v>218</v>
       </c>
@@ -2214,7 +2215,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C110"/>
+  <autoFilter ref="A1:C110">
+    <filterColumn colId="2">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/joueurs_services.xlsx
+++ b/joueurs_services.xlsx
@@ -1008,7 +1008,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:C110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -1035,7 +1034,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" hidden="1">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1046,7 +1045,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" hidden="1">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1057,7 +1056,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" hidden="1">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1068,7 +1067,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1079,7 +1078,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1090,7 +1089,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1101,7 +1100,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1112,7 +1111,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1123,7 +1122,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1142,7 +1141,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1153,7 +1152,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1164,7 +1163,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1175,7 +1174,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:3" hidden="1">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -1186,7 +1185,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1197,7 +1196,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1208,7 +1207,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1219,7 +1218,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:3" hidden="1">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -1230,7 +1229,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -1241,7 +1240,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -1252,7 +1251,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1263,7 +1262,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -1274,7 +1273,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:3" hidden="1">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>51</v>
       </c>
@@ -1285,7 +1284,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -1296,7 +1295,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:3" hidden="1">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -1307,7 +1306,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:3" hidden="1">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -1318,7 +1317,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:3" hidden="1">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>59</v>
       </c>
@@ -1329,7 +1328,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:3" hidden="1">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -1340,7 +1339,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:3" hidden="1">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1351,7 +1350,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:3" hidden="1">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -1362,7 +1361,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:3" hidden="1">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -1373,7 +1372,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:3" hidden="1">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -1384,7 +1383,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:3" hidden="1">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1395,7 +1394,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:3" hidden="1">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -1406,7 +1405,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:3" hidden="1">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -1417,7 +1416,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="38" spans="1:3" hidden="1">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -1428,7 +1427,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:3" hidden="1">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -1439,7 +1438,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:3" hidden="1">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -1450,7 +1449,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:3" hidden="1">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1461,7 +1460,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:3" hidden="1">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1472,7 +1471,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:3" hidden="1">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -1483,7 +1482,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:3" hidden="1">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -1494,7 +1493,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:3" hidden="1">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -1505,7 +1504,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:3" hidden="1">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -1516,7 +1515,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:3" hidden="1">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -1527,7 +1526,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:3" hidden="1">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>97</v>
       </c>
@@ -1538,7 +1537,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:3" hidden="1">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>99</v>
       </c>
@@ -1549,7 +1548,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>101</v>
       </c>
@@ -1560,7 +1559,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>103</v>
       </c>
@@ -1571,7 +1570,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:3" hidden="1">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>105</v>
       </c>
@@ -1582,7 +1581,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>107</v>
       </c>
@@ -1593,7 +1592,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:3" hidden="1">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>109</v>
       </c>
@@ -1604,7 +1603,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:3" hidden="1">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>111</v>
       </c>
@@ -1615,7 +1614,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:3" hidden="1">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>113</v>
       </c>
@@ -1626,7 +1625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:3" hidden="1">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>115</v>
       </c>
@@ -1637,7 +1636,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:3" hidden="1">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>117</v>
       </c>
@@ -1648,7 +1647,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:3" hidden="1">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>119</v>
       </c>
@@ -1659,7 +1658,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:3" hidden="1">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>121</v>
       </c>
@@ -1670,7 +1669,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:3" hidden="1">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>123</v>
       </c>
@@ -1681,7 +1680,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>125</v>
       </c>
@@ -1692,7 +1691,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:3" hidden="1">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>127</v>
       </c>
@@ -1703,7 +1702,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:3" hidden="1">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>129</v>
       </c>
@@ -1714,7 +1713,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:3" hidden="1">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>131</v>
       </c>
@@ -1725,7 +1724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:3" hidden="1">
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
         <v>133</v>
       </c>
@@ -1736,7 +1735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:3" hidden="1">
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>135</v>
       </c>
@@ -1747,7 +1746,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:3" hidden="1">
+    <row r="68" spans="1:3">
       <c r="A68" t="s">
         <v>137</v>
       </c>
@@ -1758,7 +1757,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="69" spans="1:3" hidden="1">
+    <row r="69" spans="1:3">
       <c r="A69" t="s">
         <v>139</v>
       </c>
@@ -1769,7 +1768,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:3" hidden="1">
+    <row r="70" spans="1:3">
       <c r="A70" t="s">
         <v>141</v>
       </c>
@@ -1780,7 +1779,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:3" hidden="1">
+    <row r="71" spans="1:3">
       <c r="A71" t="s">
         <v>143</v>
       </c>
@@ -1791,7 +1790,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:3" hidden="1">
+    <row r="72" spans="1:3">
       <c r="A72" t="s">
         <v>145</v>
       </c>
@@ -1802,7 +1801,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:3" hidden="1">
+    <row r="73" spans="1:3">
       <c r="A73" t="s">
         <v>147</v>
       </c>
@@ -1813,7 +1812,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:3" hidden="1">
+    <row r="74" spans="1:3">
       <c r="A74" t="s">
         <v>149</v>
       </c>
@@ -1824,7 +1823,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="75" spans="1:3" hidden="1">
+    <row r="75" spans="1:3">
       <c r="A75" t="s">
         <v>151</v>
       </c>
@@ -1835,7 +1834,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:3" hidden="1">
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
         <v>153</v>
       </c>
@@ -1846,7 +1845,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:3" hidden="1">
+    <row r="77" spans="1:3">
       <c r="A77" t="s">
         <v>153</v>
       </c>
@@ -1857,7 +1856,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:3" hidden="1">
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
         <v>156</v>
       </c>
@@ -1868,7 +1867,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="1:3" hidden="1">
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
         <v>158</v>
       </c>
@@ -1879,7 +1878,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:3" hidden="1">
+    <row r="80" spans="1:3">
       <c r="A80" t="s">
         <v>160</v>
       </c>
@@ -1890,7 +1889,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="81" spans="1:3" hidden="1">
+    <row r="81" spans="1:3">
       <c r="A81" t="s">
         <v>162</v>
       </c>
@@ -1901,7 +1900,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:3" hidden="1">
+    <row r="82" spans="1:3">
       <c r="A82" t="s">
         <v>164</v>
       </c>
@@ -1912,7 +1911,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:3" hidden="1">
+    <row r="83" spans="1:3">
       <c r="A83" t="s">
         <v>166</v>
       </c>
@@ -1923,7 +1922,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:3" hidden="1">
+    <row r="84" spans="1:3">
       <c r="A84" t="s">
         <v>168</v>
       </c>
@@ -1934,7 +1933,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="85" spans="1:3" hidden="1">
+    <row r="85" spans="1:3">
       <c r="A85" t="s">
         <v>170</v>
       </c>
@@ -1945,7 +1944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:3" hidden="1">
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
         <v>172</v>
       </c>
@@ -1956,7 +1955,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:3" hidden="1">
+    <row r="87" spans="1:3">
       <c r="A87" t="s">
         <v>174</v>
       </c>
@@ -1967,7 +1966,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:3" hidden="1">
+    <row r="88" spans="1:3">
       <c r="A88" t="s">
         <v>176</v>
       </c>
@@ -1978,7 +1977,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="89" spans="1:3" hidden="1">
+    <row r="89" spans="1:3">
       <c r="A89" t="s">
         <v>178</v>
       </c>
@@ -1989,7 +1988,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:3" hidden="1">
+    <row r="90" spans="1:3">
       <c r="A90" t="s">
         <v>178</v>
       </c>
@@ -2000,7 +1999,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="91" spans="1:3" hidden="1">
+    <row r="91" spans="1:3">
       <c r="A91" t="s">
         <v>181</v>
       </c>
@@ -2011,7 +2010,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:3" hidden="1">
+    <row r="92" spans="1:3">
       <c r="A92" t="s">
         <v>183</v>
       </c>
@@ -2022,7 +2021,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:3" hidden="1">
+    <row r="93" spans="1:3">
       <c r="A93" t="s">
         <v>185</v>
       </c>
@@ -2033,7 +2032,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:3" hidden="1">
+    <row r="94" spans="1:3">
       <c r="A94" t="s">
         <v>186</v>
       </c>
@@ -2044,7 +2043,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:3" hidden="1">
+    <row r="95" spans="1:3">
       <c r="A95" t="s">
         <v>188</v>
       </c>
@@ -2055,7 +2054,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:3" hidden="1">
+    <row r="96" spans="1:3">
       <c r="A96" t="s">
         <v>190</v>
       </c>
@@ -2066,7 +2065,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:3" hidden="1">
+    <row r="97" spans="1:3">
       <c r="A97" t="s">
         <v>192</v>
       </c>
@@ -2077,7 +2076,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:3" hidden="1">
+    <row r="98" spans="1:3">
       <c r="A98" t="s">
         <v>194</v>
       </c>
@@ -2088,7 +2087,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:3" hidden="1">
+    <row r="99" spans="1:3">
       <c r="A99" t="s">
         <v>196</v>
       </c>
@@ -2099,7 +2098,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:3" hidden="1">
+    <row r="100" spans="1:3">
       <c r="A100" t="s">
         <v>198</v>
       </c>
@@ -2110,7 +2109,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="101" spans="1:3" hidden="1">
+    <row r="101" spans="1:3">
       <c r="A101" t="s">
         <v>200</v>
       </c>
@@ -2121,7 +2120,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="102" spans="1:3" hidden="1">
+    <row r="102" spans="1:3">
       <c r="A102" t="s">
         <v>202</v>
       </c>
@@ -2132,7 +2131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="103" spans="1:3" hidden="1">
+    <row r="103" spans="1:3">
       <c r="A103" t="s">
         <v>204</v>
       </c>
@@ -2143,7 +2142,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="104" spans="1:3" hidden="1">
+    <row r="104" spans="1:3">
       <c r="A104" t="s">
         <v>206</v>
       </c>
@@ -2154,7 +2153,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:3" hidden="1">
+    <row r="105" spans="1:3">
       <c r="A105" t="s">
         <v>208</v>
       </c>
@@ -2173,7 +2172,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="107" spans="1:3" hidden="1">
+    <row r="107" spans="1:3">
       <c r="A107" t="s">
         <v>212</v>
       </c>
@@ -2192,7 +2191,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="109" spans="1:3" hidden="1">
+    <row r="109" spans="1:3">
       <c r="A109" t="s">
         <v>216</v>
       </c>
@@ -2203,7 +2202,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="110" spans="1:3" hidden="1">
+    <row r="110" spans="1:3">
       <c r="A110" t="s">
         <v>218</v>
       </c>
@@ -2216,9 +2215,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:C110">
-    <filterColumn colId="2">
-      <filters blank="1"/>
-    </filterColumn>
+    <filterColumn colId="2"/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
